--- a/Native_Staj_REF_Projesi_2/Challange_Performer/Data/Config.xlsx
+++ b/Native_Staj_REF_Projesi_2/Challange_Performer/Data/Config.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nisar\Desktop\native-internship-folder\Native_Staj_REF_Projesi_2\Challange_Performer\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43E9915F-73F7-4EE9-BE48-7EC7044B111F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02DCC277-EF9B-4C4E-A099-F94C61ADE7C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14616" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -165,14 +165,14 @@
     <t>RPAChallengeURL</t>
   </si>
   <si>
-    <t>"[https://www.rpachallenge.com](https://www.rpachallenge.com)"</t>
+    <t>https://www.rpachallenge.com</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -196,6 +196,12 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -214,10 +220,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -227,8 +234,10 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Köprü" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -620,7 +629,7 @@
       <c r="A6" t="s">
         <v>45</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="5" t="s">
         <v>46</v>
       </c>
     </row>
@@ -1618,8 +1627,11 @@
     <row r="998" ht="14.25" customHeight="1"/>
   </sheetData>
   <phoneticPr fontId="2"/>
+  <hyperlinks>
+    <hyperlink ref="B6" r:id="rId1" xr:uid="{25D550FE-F34F-4F40-865A-8413DC5848D7}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId2"/>
 </worksheet>
 </file>
 
